--- a/data/trans_orig/P34A_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P34A_R-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que no realiza actividad física en su tiempo libre en 2007</t>
+          <t>Población que no realiza actividad física en su tiempo libre en 2007 (tasa de respuesta: 98,45%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>283346</t>
+          <t>283620</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>334021</t>
+          <t>334378</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>41,27%</t>
+          <t>41,31%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>48,65%</t>
+          <t>48,71%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>259409</t>
+          <t>255847</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>309943</t>
+          <t>308781</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>37,91%</t>
+          <t>37,39%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>45,3%</t>
+          <t>45,13%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>557287</t>
+          <t>556156</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>626877</t>
+          <t>626866</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,7 +818,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>40,66%</t>
+          <t>40,57%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>352509</t>
+          <t>352152</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>403184</t>
+          <t>402910</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>51,35%</t>
+          <t>51,29%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>58,73%</t>
+          <t>58,69%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>374295</t>
+          <t>375457</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>424829</t>
+          <t>428391</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>54,7%</t>
+          <t>54,87%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>62,09%</t>
+          <t>62,61%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>743891</t>
+          <t>743902</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>813481</t>
+          <t>814612</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -936,7 +936,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>59,34%</t>
+          <t>59,43%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>365467</t>
+          <t>367009</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>427865</t>
+          <t>429390</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>38,67%</t>
+          <t>38,84%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>45,28%</t>
+          <t>45,44%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>420893</t>
+          <t>416934</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>480059</t>
+          <t>480301</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>44,21%</t>
+          <t>43,79%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>50,42%</t>
+          <t>50,45%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>804475</t>
+          <t>803654</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>892183</t>
+          <t>897253</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>42,41%</t>
+          <t>42,36%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>47,03%</t>
+          <t>47,3%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>517124</t>
+          <t>515599</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>579522</t>
+          <t>577980</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>54,72%</t>
+          <t>54,56%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>61,33%</t>
+          <t>61,16%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>471967</t>
+          <t>471725</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>531133</t>
+          <t>535092</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>49,58%</t>
+          <t>49,55%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>55,79%</t>
+          <t>56,21%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1004832</t>
+          <t>999762</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1092540</t>
+          <t>1093361</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>52,97%</t>
+          <t>52,7%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>57,59%</t>
+          <t>57,64%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>195485</t>
+          <t>195340</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>244199</t>
+          <t>242788</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>29,17%</t>
+          <t>29,14%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>36,43%</t>
+          <t>36,22%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>237277</t>
+          <t>240267</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>287892</t>
+          <t>289081</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>35,35%</t>
+          <t>35,79%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>42,89%</t>
+          <t>43,06%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>446744</t>
+          <t>445430</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>518816</t>
+          <t>518588</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>33,2%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>38,67%</t>
+          <t>38,66%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>426037</t>
+          <t>427448</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>474751</t>
+          <t>474896</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>63,57%</t>
+          <t>63,78%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>70,83%</t>
+          <t>70,86%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>383419</t>
+          <t>382230</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>434034</t>
+          <t>431044</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>57,11%</t>
+          <t>56,94%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>64,65%</t>
+          <t>64,21%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>822731</t>
+          <t>822959</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>894803</t>
+          <t>896117</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>61,33%</t>
+          <t>61,34%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>66,7%</t>
+          <t>66,8%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>373321</t>
+          <t>375415</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>432168</t>
+          <t>433212</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>40,15%</t>
+          <t>40,38%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>46,48%</t>
+          <t>46,59%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>506827</t>
+          <t>506900</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>570211</t>
+          <t>568100</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>50,12%</t>
+          <t>50,13%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>56,39%</t>
+          <t>56,18%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>889423</t>
+          <t>894327</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>975783</t>
+          <t>979543</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>45,82%</t>
+          <t>46,08%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>50,27%</t>
+          <t>50,47%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>497640</t>
+          <t>496596</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>556487</t>
+          <t>554393</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>53,52%</t>
+          <t>53,41%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>59,85%</t>
+          <t>59,62%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>440973</t>
+          <t>443084</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>504357</t>
+          <t>504284</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>43,61%</t>
+          <t>43,82%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>49,88%</t>
+          <t>49,87%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>965209</t>
+          <t>961449</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1051569</t>
+          <t>1046665</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>49,73%</t>
+          <t>49,53%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>54,18%</t>
+          <t>53,92%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1277681</t>
+          <t>1269057</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1387470</t>
+          <t>1384498</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>39,54%</t>
+          <t>39,27%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>42,93%</t>
+          <t>42,84%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1471330</t>
+          <t>1475908</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1592159</t>
+          <t>1591174</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>44,33%</t>
+          <t>44,47%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>47,97%</t>
+          <t>47,94%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2777688</t>
+          <t>2775725</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>2943935</t>
+          <t>2940722</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>42,41%</t>
+          <t>42,38%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>44,94%</t>
+          <t>44,89%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1844093</t>
+          <t>1847065</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1953882</t>
+          <t>1962506</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>57,07%</t>
+          <t>57,16%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>60,46%</t>
+          <t>60,73%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1726600</t>
+          <t>1727585</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1847429</t>
+          <t>1842851</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>52,03%</t>
+          <t>52,06%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>55,67%</t>
+          <t>55,53%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3606387</t>
+          <t>3609600</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>3772634</t>
+          <t>3774597</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>55,06%</t>
+          <t>55,11%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>57,59%</t>
+          <t>57,62%</t>
         </is>
       </c>
     </row>
@@ -2485,7 +2485,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que no realiza actividad física en su tiempo libre en 2012</t>
+          <t>Población que no realiza actividad física en su tiempo libre en 2012 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>139382</t>
+          <t>140763</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>185323</t>
+          <t>189122</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>19,84%</t>
+          <t>20,03%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>26,38%</t>
+          <t>26,92%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>163432</t>
+          <t>166059</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>212987</t>
+          <t>212918</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>23,45%</t>
+          <t>23,82%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>30,56%</t>
+          <t>30,55%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>319114</t>
+          <t>317716</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>385950</t>
+          <t>382909</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>22,8%</t>
+          <t>22,7%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>27,57%</t>
+          <t>27,36%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>517285</t>
+          <t>513486</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>563226</t>
+          <t>561845</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>73,62%</t>
+          <t>73,08%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>80,16%</t>
+          <t>79,97%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>484063</t>
+          <t>484132</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>533618</t>
+          <t>530991</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>69,44%</t>
+          <t>69,45%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>76,55%</t>
+          <t>76,18%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1013708</t>
+          <t>1016749</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1080544</t>
+          <t>1081942</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>72,43%</t>
+          <t>72,64%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>77,2%</t>
+          <t>77,3%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>217382</t>
+          <t>218522</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>274926</t>
+          <t>273684</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>21,35%</t>
+          <t>21,47%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>27,01%</t>
+          <t>26,89%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>344081</t>
+          <t>341551</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>404912</t>
+          <t>406766</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>33,34%</t>
+          <t>33,09%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>39,23%</t>
+          <t>39,41%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>576230</t>
+          <t>574508</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>662423</t>
+          <t>660911</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>28,11%</t>
+          <t>28,02%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>32,31%</t>
+          <t>32,24%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>743021</t>
+          <t>744263</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>800565</t>
+          <t>799425</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>72,99%</t>
+          <t>73,11%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>78,65%</t>
+          <t>78,53%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>627272</t>
+          <t>625418</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>688103</t>
+          <t>690633</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>60,77%</t>
+          <t>60,59%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>66,66%</t>
+          <t>66,91%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1387708</t>
+          <t>1389220</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1473901</t>
+          <t>1475623</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>67,69%</t>
+          <t>67,76%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>71,89%</t>
+          <t>71,98%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>135563</t>
+          <t>135227</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>181698</t>
+          <t>182717</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>17,89%</t>
+          <t>17,85%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>23,98%</t>
+          <t>24,12%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>192095</t>
+          <t>193773</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>245157</t>
+          <t>245187</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,7 +3416,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>24,75%</t>
+          <t>24,97%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>340692</t>
+          <t>340249</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>415570</t>
+          <t>409311</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>22,21%</t>
+          <t>22,18%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>27,1%</t>
+          <t>26,69%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>575925</t>
+          <t>574906</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>622060</t>
+          <t>622396</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>76,02%</t>
+          <t>75,88%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>82,11%</t>
+          <t>82,15%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>530919</t>
+          <t>530889</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>583981</t>
+          <t>582303</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3534,7 +3534,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>75,25%</t>
+          <t>75,03%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1118130</t>
+          <t>1124389</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1193008</t>
+          <t>1193451</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>72,9%</t>
+          <t>73,31%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>77,79%</t>
+          <t>77,82%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>180558</t>
+          <t>180828</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>232275</t>
+          <t>232621</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>19,07%</t>
+          <t>19,1%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>24,53%</t>
+          <t>24,57%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>290401</t>
+          <t>286486</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>348270</t>
+          <t>344475</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>27,61%</t>
+          <t>27,24%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>33,11%</t>
+          <t>32,75%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>482916</t>
+          <t>480300</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>565409</t>
+          <t>563969</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>24,16%</t>
+          <t>24,03%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>28,29%</t>
+          <t>28,22%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>714567</t>
+          <t>714221</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>766284</t>
+          <t>766014</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>75,47%</t>
+          <t>75,43%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>80,93%</t>
+          <t>80,9%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>703631</t>
+          <t>707426</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>761500</t>
+          <t>765415</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>66,89%</t>
+          <t>67,25%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>72,39%</t>
+          <t>72,76%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1433334</t>
+          <t>1434774</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1515827</t>
+          <t>1518443</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>71,71%</t>
+          <t>71,78%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>75,84%</t>
+          <t>75,97%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>720971</t>
+          <t>719512</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>825293</t>
+          <t>820113</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>21,05%</t>
+          <t>21,01%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>24,1%</t>
+          <t>23,94%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1042002</t>
+          <t>1045472</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1157285</t>
+          <t>1157918</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>29,29%</t>
+          <t>29,39%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>32,53%</t>
+          <t>32,55%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1796791</t>
+          <t>1793702</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1940903</t>
+          <t>1945254</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>25,73%</t>
+          <t>25,69%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>27,8%</t>
+          <t>27,86%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2599728</t>
+          <t>2604908</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2704050</t>
+          <t>2705509</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>75,9%</t>
+          <t>76,06%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>78,95%</t>
+          <t>78,99%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2399926</t>
+          <t>2399293</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2515209</t>
+          <t>2511739</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>67,47%</t>
+          <t>67,45%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>70,71%</t>
+          <t>70,61%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5041329</t>
+          <t>5036978</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5185441</t>
+          <t>5188530</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>72,2%</t>
+          <t>72,14%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>74,27%</t>
+          <t>74,31%</t>
         </is>
       </c>
     </row>
@@ -4432,7 +4432,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que no realiza actividad física en su tiempo libre en 2016</t>
+          <t>Población que no realiza actividad física en su tiempo libre en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>211741</t>
+          <t>213577</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>264147</t>
+          <t>264932</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>31,38%</t>
+          <t>31,65%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>39,14%</t>
+          <t>39,26%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>284475</t>
+          <t>283703</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>335060</t>
+          <t>333046</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>42,28%</t>
+          <t>42,17%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>49,8%</t>
+          <t>49,5%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>512339</t>
+          <t>514652</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>589506</t>
+          <t>585395</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>38,02%</t>
+          <t>38,19%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>43,74%</t>
+          <t>43,44%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>410653</t>
+          <t>409868</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>463059</t>
+          <t>461223</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>60,86%</t>
+          <t>60,74%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>68,62%</t>
+          <t>68,35%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>337779</t>
+          <t>339793</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>388364</t>
+          <t>389136</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>50,2%</t>
+          <t>50,5%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>57,72%</t>
+          <t>57,83%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>758133</t>
+          <t>762244</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>835300</t>
+          <t>832987</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>56,26%</t>
+          <t>56,56%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>61,98%</t>
+          <t>61,81%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>332117</t>
+          <t>327719</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>394731</t>
+          <t>389775</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>32,48%</t>
+          <t>32,05%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>38,61%</t>
+          <t>38,12%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>415214</t>
+          <t>418435</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>481108</t>
+          <t>483421</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>39,81%</t>
+          <t>40,12%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>46,13%</t>
+          <t>46,35%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>759400</t>
+          <t>757817</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>851480</t>
+          <t>852983</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>36,77%</t>
+          <t>36,69%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>41,23%</t>
+          <t>41,3%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>627700</t>
+          <t>632656</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>690314</t>
+          <t>694712</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>61,39%</t>
+          <t>61,88%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>67,52%</t>
+          <t>67,95%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>561805</t>
+          <t>559492</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>627699</t>
+          <t>624478</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>53,87%</t>
+          <t>53,65%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>60,19%</t>
+          <t>59,88%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1213864</t>
+          <t>1212361</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1305944</t>
+          <t>1307527</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>58,77%</t>
+          <t>58,7%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>63,23%</t>
+          <t>63,31%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>225450</t>
+          <t>227936</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>279576</t>
+          <t>281608</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>29,68%</t>
+          <t>30,01%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>36,81%</t>
+          <t>37,08%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>283148</t>
+          <t>285882</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>339690</t>
+          <t>341704</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>36,07%</t>
+          <t>36,42%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>43,27%</t>
+          <t>43,53%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>526438</t>
+          <t>524974</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>604857</t>
+          <t>603625</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>34,08%</t>
+          <t>33,99%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>39,16%</t>
+          <t>39,08%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>479976</t>
+          <t>477944</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>534102</t>
+          <t>531616</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>63,19%</t>
+          <t>62,92%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>70,32%</t>
+          <t>69,99%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>445321</t>
+          <t>443307</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>501863</t>
+          <t>499129</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>56,73%</t>
+          <t>56,47%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>63,93%</t>
+          <t>63,58%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>939706</t>
+          <t>940938</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1018125</t>
+          <t>1019589</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>60,84%</t>
+          <t>60,92%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>65,92%</t>
+          <t>66,01%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>271296</t>
+          <t>272356</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>327861</t>
+          <t>330771</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>28,94%</t>
+          <t>29,05%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>34,97%</t>
+          <t>35,28%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>413040</t>
+          <t>409581</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>478115</t>
+          <t>479916</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>39,57%</t>
+          <t>39,24%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>45,81%</t>
+          <t>45,98%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>704838</t>
+          <t>699144</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>790196</t>
+          <t>783797</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>35,57%</t>
+          <t>35,29%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>39,88%</t>
+          <t>39,56%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>609706</t>
+          <t>606796</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>666271</t>
+          <t>665211</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>65,03%</t>
+          <t>64,72%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>71,06%</t>
+          <t>70,95%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>565664</t>
+          <t>563863</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>630739</t>
+          <t>634198</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>54,19%</t>
+          <t>54,02%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>60,43%</t>
+          <t>60,76%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1191150</t>
+          <t>1197549</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1276508</t>
+          <t>1282202</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>60,12%</t>
+          <t>60,44%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>64,43%</t>
+          <t>64,71%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1091965</t>
+          <t>1093989</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1204174</t>
+          <t>1211924</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>32,17%</t>
+          <t>32,23%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>35,48%</t>
+          <t>35,7%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1451762</t>
+          <t>1455725</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1571420</t>
+          <t>1574322</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>40,96%</t>
+          <t>41,07%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>44,33%</t>
+          <t>44,42%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2570329</t>
+          <t>2579108</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>2735966</t>
+          <t>2745765</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>37,04%</t>
+          <t>37,17%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>39,43%</t>
+          <t>39,57%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2190176</t>
+          <t>2182426</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2302385</t>
+          <t>2300361</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>64,52%</t>
+          <t>64,3%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>67,83%</t>
+          <t>67,77%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1973122</t>
+          <t>1970220</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2092780</t>
+          <t>2088817</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>55,67%</t>
+          <t>55,58%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>59,04%</t>
+          <t>58,93%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4202926</t>
+          <t>4193127</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>4368563</t>
+          <t>4359784</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>60,57%</t>
+          <t>60,43%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>62,96%</t>
+          <t>62,83%</t>
         </is>
       </c>
     </row>
@@ -6379,7 +6379,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que no realiza actividad física en su tiempo libre en 2023</t>
+          <t>Población que no realiza actividad física en su tiempo libre en 2023 (tasa de respuesta: 99,76%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6574,12 +6574,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>218388</t>
+          <t>218058</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>272029</t>
+          <t>271462</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>34,51%</t>
+          <t>34,45%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>42,98%</t>
+          <t>42,89%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6609,12 +6609,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>238708</t>
+          <t>239912</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>279416</t>
+          <t>279296</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>35,36%</t>
+          <t>35,54%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>41,4%</t>
+          <t>41,38%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>468440</t>
+          <t>469846</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>537061</t>
+          <t>535309</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6659,12 +6659,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>35,82%</t>
+          <t>35,92%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>41,06%</t>
+          <t>40,93%</t>
         </is>
       </c>
     </row>
@@ -6687,12 +6687,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>360864</t>
+          <t>361431</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>414505</t>
+          <t>414835</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>57,02%</t>
+          <t>57,11%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>65,49%</t>
+          <t>65,55%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6722,12 +6722,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>395577</t>
+          <t>395697</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>436285</t>
+          <t>435081</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>58,6%</t>
+          <t>58,62%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>64,64%</t>
+          <t>64,46%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>770825</t>
+          <t>772577</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>839446</t>
+          <t>838040</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6772,12 +6772,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>58,94%</t>
+          <t>59,07%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>64,18%</t>
+          <t>64,08%</t>
         </is>
       </c>
     </row>
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>174806</t>
+          <t>159968</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>408954</t>
+          <t>407707</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,69%</t>
+          <t>13,44%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>34,36%</t>
+          <t>34,26%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>343461</t>
+          <t>341853</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>397446</t>
+          <t>394875</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>35,88%</t>
+          <t>35,71%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>41,51%</t>
+          <t>41,25%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>461589</t>
+          <t>438397</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>783420</t>
+          <t>783687</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>21,49%</t>
+          <t>20,41%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>36,48%</t>
+          <t>36,49%</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>781229</t>
+          <t>782476</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1015377</t>
+          <t>1030215</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>65,64%</t>
+          <t>65,74%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>85,31%</t>
+          <t>86,56%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>559920</t>
+          <t>562491</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>613905</t>
+          <t>615513</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>58,49%</t>
+          <t>58,75%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>64,12%</t>
+          <t>64,29%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1364129</t>
+          <t>1363862</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1685960</t>
+          <t>1709152</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>63,52%</t>
+          <t>63,51%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>78,51%</t>
+          <t>79,59%</t>
         </is>
       </c>
     </row>
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>214450</t>
+          <t>212816</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>270152</t>
+          <t>269594</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>30,48%</t>
+          <t>30,25%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>38,39%</t>
+          <t>38,31%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>178820</t>
+          <t>181353</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>463624</t>
+          <t>465653</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19,21%</t>
+          <t>19,48%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>49,8%</t>
+          <t>50,01%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>368607</t>
+          <t>398693</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>693280</t>
+          <t>698011</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>22,55%</t>
+          <t>24,39%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>42,41%</t>
+          <t>42,7%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>433479</t>
+          <t>434037</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>489181</t>
+          <t>490815</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>61,61%</t>
+          <t>61,69%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>69,52%</t>
+          <t>69,75%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>467429</t>
+          <t>465400</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>752233</t>
+          <t>749700</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>50,2%</t>
+          <t>49,99%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>80,79%</t>
+          <t>80,52%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>941403</t>
+          <t>936672</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1266076</t>
+          <t>1235990</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>57,59%</t>
+          <t>57,3%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>77,45%</t>
+          <t>75,61%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>240220</t>
+          <t>239540</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>298414</t>
+          <t>297877</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>26,0%</t>
+          <t>25,93%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>32,3%</t>
+          <t>32,24%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>334475</t>
+          <t>341081</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>452991</t>
+          <t>456696</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>30,69%</t>
+          <t>31,3%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>41,57%</t>
+          <t>41,91%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>608302</t>
+          <t>611493</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>732443</t>
+          <t>733128</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>30,21%</t>
+          <t>30,37%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>36,37%</t>
+          <t>36,41%</t>
         </is>
       </c>
     </row>
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>625426</t>
+          <t>625963</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>683620</t>
+          <t>684300</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>67,7%</t>
+          <t>67,76%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>74,0%</t>
+          <t>74,07%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>636845</t>
+          <t>633140</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>755361</t>
+          <t>748755</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>58,43%</t>
+          <t>58,09%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>69,31%</t>
+          <t>68,7%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1281233</t>
+          <t>1280548</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1405374</t>
+          <t>1402183</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>63,63%</t>
+          <t>63,59%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>69,79%</t>
+          <t>69,63%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>804984</t>
+          <t>822048</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1168999</t>
+          <t>1173211</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>23,33%</t>
+          <t>23,82%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>33,88%</t>
+          <t>34,0%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1129133</t>
+          <t>1124899</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1500600</t>
+          <t>1504516</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>30,91%</t>
+          <t>30,79%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>41,08%</t>
+          <t>41,18%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2136716</t>
+          <t>2135725</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>2634551</t>
+          <t>2627855</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>30,08%</t>
+          <t>30,06%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>37,09%</t>
+          <t>36,99%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2281547</t>
+          <t>2277335</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2645562</t>
+          <t>2628498</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>66,12%</t>
+          <t>66,0%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>76,67%</t>
+          <t>76,18%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2152648</t>
+          <t>2148732</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2524115</t>
+          <t>2528349</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>58,92%</t>
+          <t>58,82%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>69,09%</t>
+          <t>69,21%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4469243</t>
+          <t>4475939</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>4967078</t>
+          <t>4968069</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>62,91%</t>
+          <t>63,01%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>69,92%</t>
+          <t>69,94%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P34A_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P34A_R-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>283620</t>
+          <t>284112</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>334378</t>
+          <t>338112</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>41,31%</t>
+          <t>41,38%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>48,71%</t>
+          <t>49,25%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>255847</t>
+          <t>258553</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>308781</t>
+          <t>309320</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>37,39%</t>
+          <t>37,79%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>45,13%</t>
+          <t>45,21%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>556156</t>
+          <t>554670</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>626866</t>
+          <t>626942</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>40,57%</t>
+          <t>40,46%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>45,73%</t>
+          <t>45,74%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>352152</t>
+          <t>348418</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>402910</t>
+          <t>402418</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>51,29%</t>
+          <t>50,75%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>58,69%</t>
+          <t>58,62%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>375457</t>
+          <t>374918</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>428391</t>
+          <t>425685</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>54,87%</t>
+          <t>54,79%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>62,61%</t>
+          <t>62,21%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>743902</t>
+          <t>743826</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>814612</t>
+          <t>816098</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>54,27%</t>
+          <t>54,26%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>59,43%</t>
+          <t>59,54%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>367009</t>
+          <t>368823</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>429390</t>
+          <t>429382</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>38,84%</t>
+          <t>39,03%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>416934</t>
+          <t>414124</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>480301</t>
+          <t>478692</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>43,79%</t>
+          <t>43,5%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>50,45%</t>
+          <t>50,28%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>803654</t>
+          <t>801683</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>897253</t>
+          <t>886687</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>42,36%</t>
+          <t>42,26%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>47,3%</t>
+          <t>46,74%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>515599</t>
+          <t>515607</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>577980</t>
+          <t>576166</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1209,7 +1209,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>61,16%</t>
+          <t>60,97%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>471725</t>
+          <t>473334</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>535092</t>
+          <t>537902</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>49,55%</t>
+          <t>49,72%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>56,21%</t>
+          <t>56,5%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>999762</t>
+          <t>1010328</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1093361</t>
+          <t>1095332</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>52,7%</t>
+          <t>53,26%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>57,64%</t>
+          <t>57,74%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>195340</t>
+          <t>194257</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>242788</t>
+          <t>244011</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>29,14%</t>
+          <t>28,98%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>36,22%</t>
+          <t>36,41%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>240267</t>
+          <t>239992</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>289081</t>
+          <t>288234</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>35,79%</t>
+          <t>35,75%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>43,06%</t>
+          <t>42,94%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>445430</t>
+          <t>446905</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>518588</t>
+          <t>518366</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>33,2%</t>
+          <t>33,31%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>38,66%</t>
+          <t>38,64%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>427448</t>
+          <t>426225</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>474896</t>
+          <t>475979</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>63,78%</t>
+          <t>63,59%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>70,86%</t>
+          <t>71,02%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>382230</t>
+          <t>383077</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>431044</t>
+          <t>431319</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>56,94%</t>
+          <t>57,06%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>64,21%</t>
+          <t>64,25%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>822959</t>
+          <t>823181</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>896117</t>
+          <t>894642</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>61,34%</t>
+          <t>61,36%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>66,8%</t>
+          <t>66,69%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>375415</t>
+          <t>373525</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>433212</t>
+          <t>435305</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>40,38%</t>
+          <t>40,17%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>46,59%</t>
+          <t>46,82%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>506900</t>
+          <t>505542</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>568100</t>
+          <t>568334</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>50,13%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>56,18%</t>
+          <t>56,2%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>894327</t>
+          <t>892661</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>979543</t>
+          <t>980080</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>46,08%</t>
+          <t>45,99%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>50,47%</t>
+          <t>50,49%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>496596</t>
+          <t>494503</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>554393</t>
+          <t>556283</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>53,41%</t>
+          <t>53,18%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>59,62%</t>
+          <t>59,83%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>443084</t>
+          <t>442850</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>504284</t>
+          <t>505642</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>43,82%</t>
+          <t>43,8%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>49,87%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>961449</t>
+          <t>960912</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1046665</t>
+          <t>1048331</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>49,53%</t>
+          <t>49,51%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>53,92%</t>
+          <t>54,01%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1269057</t>
+          <t>1266243</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1384498</t>
+          <t>1378935</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>39,27%</t>
+          <t>39,18%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>42,84%</t>
+          <t>42,67%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1475908</t>
+          <t>1472231</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1591174</t>
+          <t>1591192</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>44,47%</t>
+          <t>44,36%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>47,94%</t>
+          <t>47,95%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2775725</t>
+          <t>2778487</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>2940722</t>
+          <t>2944256</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>42,38%</t>
+          <t>42,42%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>44,89%</t>
+          <t>44,95%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1847065</t>
+          <t>1852628</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1962506</t>
+          <t>1965320</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>57,16%</t>
+          <t>57,33%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>60,73%</t>
+          <t>60,82%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1727585</t>
+          <t>1727567</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1842851</t>
+          <t>1846528</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>52,06%</t>
+          <t>52,05%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>55,53%</t>
+          <t>55,64%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3609600</t>
+          <t>3606066</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>3774597</t>
+          <t>3771835</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>55,11%</t>
+          <t>55,05%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>57,62%</t>
+          <t>57,58%</t>
         </is>
       </c>
     </row>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>140763</t>
+          <t>141160</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>189122</t>
+          <t>186417</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>20,03%</t>
+          <t>20,09%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>26,92%</t>
+          <t>26,53%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>166059</t>
+          <t>165859</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>212918</t>
+          <t>213244</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>23,82%</t>
+          <t>23,79%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>30,55%</t>
+          <t>30,59%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>317716</t>
+          <t>321186</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>382909</t>
+          <t>388306</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>22,7%</t>
+          <t>22,95%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>27,36%</t>
+          <t>27,74%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>513486</t>
+          <t>516191</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>561845</t>
+          <t>561448</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>73,08%</t>
+          <t>73,47%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>79,97%</t>
+          <t>79,91%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>484132</t>
+          <t>483806</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>530991</t>
+          <t>531191</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>69,45%</t>
+          <t>69,41%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>76,18%</t>
+          <t>76,21%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1016749</t>
+          <t>1011352</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1081942</t>
+          <t>1078472</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>72,64%</t>
+          <t>72,26%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>77,3%</t>
+          <t>77,05%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>218522</t>
+          <t>216057</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>273684</t>
+          <t>274893</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>21,47%</t>
+          <t>21,22%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>26,89%</t>
+          <t>27,0%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>341551</t>
+          <t>344284</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>406766</t>
+          <t>407734</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>33,09%</t>
+          <t>33,35%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>39,41%</t>
+          <t>39,5%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>574508</t>
+          <t>579370</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>660911</t>
+          <t>663323</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>28,02%</t>
+          <t>28,26%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>32,24%</t>
+          <t>32,36%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>744263</t>
+          <t>743054</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>799425</t>
+          <t>801890</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>73,11%</t>
+          <t>73,0%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>78,53%</t>
+          <t>78,78%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>625418</t>
+          <t>624450</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>690633</t>
+          <t>687900</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>60,59%</t>
+          <t>60,5%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>66,91%</t>
+          <t>66,65%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1389220</t>
+          <t>1386808</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1475623</t>
+          <t>1470761</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>67,76%</t>
+          <t>67,64%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>71,98%</t>
+          <t>71,74%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>135227</t>
+          <t>133810</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>182717</t>
+          <t>178940</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>17,85%</t>
+          <t>17,66%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>24,12%</t>
+          <t>23,62%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>193773</t>
+          <t>194599</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>245187</t>
+          <t>248959</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>24,97%</t>
+          <t>25,07%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>31,59%</t>
+          <t>32,08%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>340249</t>
+          <t>345990</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>409311</t>
+          <t>414073</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>22,18%</t>
+          <t>22,56%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>26,69%</t>
+          <t>27,0%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>574906</t>
+          <t>578683</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>622396</t>
+          <t>623813</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>75,88%</t>
+          <t>76,38%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>82,15%</t>
+          <t>82,34%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>530889</t>
+          <t>527117</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>582303</t>
+          <t>581477</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>68,41%</t>
+          <t>67,92%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>75,03%</t>
+          <t>74,93%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1124389</t>
+          <t>1119627</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1193451</t>
+          <t>1187710</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>73,31%</t>
+          <t>73,0%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>77,82%</t>
+          <t>77,44%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>180828</t>
+          <t>181672</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>232621</t>
+          <t>233007</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>19,1%</t>
+          <t>19,19%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>24,57%</t>
+          <t>24,61%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>286486</t>
+          <t>291849</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>344475</t>
+          <t>349422</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>27,24%</t>
+          <t>27,74%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>32,75%</t>
+          <t>33,22%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>480300</t>
+          <t>486746</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>563969</t>
+          <t>568759</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>24,03%</t>
+          <t>24,35%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>28,22%</t>
+          <t>28,46%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>714221</t>
+          <t>713835</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>766014</t>
+          <t>765170</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>75,43%</t>
+          <t>75,39%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>80,9%</t>
+          <t>80,81%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>707426</t>
+          <t>702479</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>765415</t>
+          <t>760052</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>67,25%</t>
+          <t>66,78%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>72,76%</t>
+          <t>72,26%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1434774</t>
+          <t>1429984</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1518443</t>
+          <t>1511997</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>71,78%</t>
+          <t>71,54%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>75,97%</t>
+          <t>75,65%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>719512</t>
+          <t>719529</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>820113</t>
+          <t>818528</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4072,7 +4072,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>23,94%</t>
+          <t>23,9%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1045472</t>
+          <t>1041111</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1157918</t>
+          <t>1153592</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>29,39%</t>
+          <t>29,27%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>32,55%</t>
+          <t>32,43%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1793702</t>
+          <t>1797037</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1945254</t>
+          <t>1943348</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>25,69%</t>
+          <t>25,74%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>27,86%</t>
+          <t>27,83%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2604908</t>
+          <t>2606493</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2705509</t>
+          <t>2705492</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,7 +4180,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>76,06%</t>
+          <t>76,1%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2399293</t>
+          <t>2403619</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2511739</t>
+          <t>2516100</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>67,45%</t>
+          <t>67,57%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>70,61%</t>
+          <t>70,73%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5036978</t>
+          <t>5038884</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5188530</t>
+          <t>5185195</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>72,14%</t>
+          <t>72,17%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>74,31%</t>
+          <t>74,26%</t>
         </is>
       </c>
     </row>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>213577</t>
+          <t>213606</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>264932</t>
+          <t>264736</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4647,7 +4647,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>39,26%</t>
+          <t>39,23%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>283703</t>
+          <t>283959</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>333046</t>
+          <t>334504</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>42,17%</t>
+          <t>42,2%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>49,5%</t>
+          <t>49,72%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>514652</t>
+          <t>511938</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>585395</t>
+          <t>585820</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>38,19%</t>
+          <t>37,99%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>43,44%</t>
+          <t>43,47%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>409868</t>
+          <t>410064</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>461223</t>
+          <t>461194</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,7 +4755,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>60,74%</t>
+          <t>60,77%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>339793</t>
+          <t>338335</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>389136</t>
+          <t>388880</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>50,5%</t>
+          <t>50,28%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>57,83%</t>
+          <t>57,8%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>762244</t>
+          <t>761819</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>832987</t>
+          <t>835701</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>56,56%</t>
+          <t>56,53%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>61,81%</t>
+          <t>62,01%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>327719</t>
+          <t>326616</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>389775</t>
+          <t>387940</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>32,05%</t>
+          <t>31,95%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>38,12%</t>
+          <t>37,94%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>418435</t>
+          <t>413848</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>483421</t>
+          <t>480042</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>40,12%</t>
+          <t>39,68%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>46,35%</t>
+          <t>46,03%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>757817</t>
+          <t>760513</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>852983</t>
+          <t>856507</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>36,69%</t>
+          <t>36,82%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>41,3%</t>
+          <t>41,47%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>632656</t>
+          <t>634491</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>694712</t>
+          <t>695815</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>61,88%</t>
+          <t>62,06%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>67,95%</t>
+          <t>68,05%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>559492</t>
+          <t>562871</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>624478</t>
+          <t>629065</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>53,65%</t>
+          <t>53,97%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>59,88%</t>
+          <t>60,32%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1212361</t>
+          <t>1208837</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1307527</t>
+          <t>1304831</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>58,7%</t>
+          <t>58,53%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>63,31%</t>
+          <t>63,18%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>227936</t>
+          <t>227152</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>281608</t>
+          <t>279964</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>30,01%</t>
+          <t>29,91%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>37,08%</t>
+          <t>36,86%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>285882</t>
+          <t>285921</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>341704</t>
+          <t>342027</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5368,7 +5368,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>43,53%</t>
+          <t>43,57%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>524974</t>
+          <t>525249</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>603625</t>
+          <t>602873</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>33,99%</t>
+          <t>34,01%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>39,08%</t>
+          <t>39,03%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>477944</t>
+          <t>479588</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>531616</t>
+          <t>532400</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>62,92%</t>
+          <t>63,14%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>69,99%</t>
+          <t>70,09%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>443307</t>
+          <t>442984</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>499129</t>
+          <t>499090</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,7 +5476,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>56,47%</t>
+          <t>56,43%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>940938</t>
+          <t>941690</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1019589</t>
+          <t>1019314</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>60,92%</t>
+          <t>60,97%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>66,01%</t>
+          <t>65,99%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>272356</t>
+          <t>271980</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>330771</t>
+          <t>329701</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>29,05%</t>
+          <t>29,01%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>35,28%</t>
+          <t>35,17%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>409581</t>
+          <t>413747</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>479916</t>
+          <t>478419</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>39,24%</t>
+          <t>39,64%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>45,98%</t>
+          <t>45,84%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>699144</t>
+          <t>698509</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>783797</t>
+          <t>784786</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>35,29%</t>
+          <t>35,25%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>39,56%</t>
+          <t>39,61%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>606796</t>
+          <t>607866</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>665211</t>
+          <t>665587</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>64,72%</t>
+          <t>64,83%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>70,95%</t>
+          <t>70,99%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>563863</t>
+          <t>565360</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>634198</t>
+          <t>630032</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>54,02%</t>
+          <t>54,16%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>60,76%</t>
+          <t>60,36%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1197549</t>
+          <t>1196560</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1282202</t>
+          <t>1282837</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>60,44%</t>
+          <t>60,39%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>64,71%</t>
+          <t>64,75%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1093989</t>
+          <t>1092772</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1211924</t>
+          <t>1209112</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>32,23%</t>
+          <t>32,19%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>35,7%</t>
+          <t>35,62%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1455725</t>
+          <t>1458520</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1574322</t>
+          <t>1578005</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>41,07%</t>
+          <t>41,15%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>44,42%</t>
+          <t>44,52%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2579108</t>
+          <t>2589110</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>2745765</t>
+          <t>2748514</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>37,17%</t>
+          <t>37,31%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>39,57%</t>
+          <t>39,61%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2182426</t>
+          <t>2185238</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2300361</t>
+          <t>2301578</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>64,3%</t>
+          <t>64,38%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>67,77%</t>
+          <t>67,81%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1970220</t>
+          <t>1966537</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2088817</t>
+          <t>2086022</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>55,58%</t>
+          <t>55,48%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>58,93%</t>
+          <t>58,85%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4193127</t>
+          <t>4190378</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>4359784</t>
+          <t>4349782</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>60,43%</t>
+          <t>60,39%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>62,83%</t>
+          <t>62,69%</t>
         </is>
       </c>
     </row>
@@ -6569,32 +6569,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>243944</t>
+          <t>268998</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>218058</t>
+          <t>238898</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>271462</t>
+          <t>297969</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>38,54%</t>
+          <t>39,12%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>34,45%</t>
+          <t>34,74%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>42,89%</t>
+          <t>43,33%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6604,32 +6604,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>258789</t>
+          <t>282673</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>239912</t>
+          <t>261837</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>279296</t>
+          <t>306136</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>38,34%</t>
+          <t>38,6%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>35,54%</t>
+          <t>35,75%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>41,38%</t>
+          <t>41,8%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>502734</t>
+          <t>551671</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>469846</t>
+          <t>516847</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>535309</t>
+          <t>586113</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>38,44%</t>
+          <t>38,85%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>35,92%</t>
+          <t>36,4%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>40,93%</t>
+          <t>41,28%</t>
         </is>
       </c>
     </row>
@@ -6682,32 +6682,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>388949</t>
+          <t>418634</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>361431</t>
+          <t>389663</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>414835</t>
+          <t>448734</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>61,46%</t>
+          <t>60,88%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>57,11%</t>
+          <t>56,67%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>65,55%</t>
+          <t>65,26%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6717,32 +6717,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>416204</t>
+          <t>449661</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>395697</t>
+          <t>426198</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>435081</t>
+          <t>470497</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>61,66%</t>
+          <t>61,4%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>58,62%</t>
+          <t>58,2%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>64,46%</t>
+          <t>64,25%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>805152</t>
+          <t>868295</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>772577</t>
+          <t>833853</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>838040</t>
+          <t>903119</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>61,56%</t>
+          <t>61,15%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>59,07%</t>
+          <t>58,72%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>64,08%</t>
+          <t>63,6%</t>
         </is>
       </c>
     </row>
@@ -6795,17 +6795,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>632893</t>
+          <t>687632</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>632893</t>
+          <t>687632</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>632893</t>
+          <t>687632</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6830,17 +6830,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>674993</t>
+          <t>732334</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>674993</t>
+          <t>732334</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>674993</t>
+          <t>732334</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1307886</t>
+          <t>1419966</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1307886</t>
+          <t>1419966</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1307886</t>
+          <t>1419966</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6912,32 +6912,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>313592</t>
+          <t>347265</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>159968</t>
+          <t>314448</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>407707</t>
+          <t>382408</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>26,35%</t>
+          <t>33,19%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>30,06%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>34,26%</t>
+          <t>36,55%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6947,32 +6947,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>368422</t>
+          <t>410881</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>341853</t>
+          <t>380757</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>394875</t>
+          <t>439368</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>38,48%</t>
+          <t>38,42%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>35,71%</t>
+          <t>35,6%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>41,25%</t>
+          <t>41,08%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>682014</t>
+          <t>758146</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>438397</t>
+          <t>711233</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>783687</t>
+          <t>802327</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>31,76%</t>
+          <t>35,83%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>20,41%</t>
+          <t>33,62%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>36,49%</t>
+          <t>37,92%</t>
         </is>
       </c>
     </row>
@@ -7025,32 +7025,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>876591</t>
+          <t>698923</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>782476</t>
+          <t>663780</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1030215</t>
+          <t>731740</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>73,65%</t>
+          <t>66,81%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>65,74%</t>
+          <t>63,45%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>86,56%</t>
+          <t>69,94%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7060,32 +7060,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>588944</t>
+          <t>658644</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>562491</t>
+          <t>630157</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>615513</t>
+          <t>688768</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>61,52%</t>
+          <t>61,58%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>58,75%</t>
+          <t>58,92%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>64,29%</t>
+          <t>64,4%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1465535</t>
+          <t>1357568</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1363862</t>
+          <t>1313387</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1709152</t>
+          <t>1404481</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>68,24%</t>
+          <t>64,17%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>63,51%</t>
+          <t>62,08%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>79,59%</t>
+          <t>66,38%</t>
         </is>
       </c>
     </row>
@@ -7138,17 +7138,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1190183</t>
+          <t>1046188</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1190183</t>
+          <t>1046188</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1190183</t>
+          <t>1046188</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7173,17 +7173,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>957366</t>
+          <t>1069525</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>957366</t>
+          <t>1069525</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>957366</t>
+          <t>1069525</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>2147549</t>
+          <t>2115714</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2147549</t>
+          <t>2115714</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2147549</t>
+          <t>2115714</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7255,32 +7255,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>239711</t>
+          <t>281236</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>212816</t>
+          <t>254071</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>269594</t>
+          <t>314840</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>34,07%</t>
+          <t>35,07%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>30,25%</t>
+          <t>31,68%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>38,31%</t>
+          <t>39,26%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7290,32 +7290,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>347823</t>
+          <t>363584</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>181353</t>
+          <t>339321</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>465653</t>
+          <t>392056</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>37,36%</t>
+          <t>44,92%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19,48%</t>
+          <t>41,92%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>50,01%</t>
+          <t>48,43%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>587534</t>
+          <t>644819</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>398693</t>
+          <t>604423</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>698011</t>
+          <t>686507</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>35,94%</t>
+          <t>40,02%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>24,39%</t>
+          <t>37,51%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>42,7%</t>
+          <t>42,6%</t>
         </is>
       </c>
     </row>
@@ -7368,32 +7368,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>463920</t>
+          <t>520708</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>434037</t>
+          <t>487104</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>490815</t>
+          <t>547873</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>65,93%</t>
+          <t>64,93%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>61,69%</t>
+          <t>60,74%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>69,75%</t>
+          <t>68,32%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7403,32 +7403,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>583230</t>
+          <t>445867</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>465400</t>
+          <t>417395</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>749700</t>
+          <t>470130</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>62,64%</t>
+          <t>55,08%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>49,99%</t>
+          <t>51,57%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>80,52%</t>
+          <t>58,08%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1047149</t>
+          <t>966576</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>936672</t>
+          <t>924888</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1235990</t>
+          <t>1006972</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>64,06%</t>
+          <t>59,98%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>57,3%</t>
+          <t>57,4%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>75,61%</t>
+          <t>62,49%</t>
         </is>
       </c>
     </row>
@@ -7481,17 +7481,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>703631</t>
+          <t>801944</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>703631</t>
+          <t>801944</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>703631</t>
+          <t>801944</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7516,17 +7516,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>931053</t>
+          <t>809451</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>931053</t>
+          <t>809451</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>931053</t>
+          <t>809451</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1634683</t>
+          <t>1611395</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1634683</t>
+          <t>1611395</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1634683</t>
+          <t>1611395</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7598,32 +7598,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>268855</t>
+          <t>280806</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>239540</t>
+          <t>252097</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>297877</t>
+          <t>311232</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>29,1%</t>
+          <t>28,45%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>25,93%</t>
+          <t>25,54%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>32,24%</t>
+          <t>31,53%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7633,32 +7633,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>411977</t>
+          <t>451693</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>341081</t>
+          <t>424727</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>456696</t>
+          <t>480987</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>37,8%</t>
+          <t>40,52%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>31,3%</t>
+          <t>38,1%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>41,91%</t>
+          <t>43,15%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>680832</t>
+          <t>732499</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>611493</t>
+          <t>689752</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>733128</t>
+          <t>770251</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>33,81%</t>
+          <t>34,85%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>30,37%</t>
+          <t>32,82%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>36,41%</t>
+          <t>36,65%</t>
         </is>
       </c>
     </row>
@@ -7711,32 +7711,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>654985</t>
+          <t>706223</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>625963</t>
+          <t>675797</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>684300</t>
+          <t>734932</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>70,9%</t>
+          <t>71,55%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>67,76%</t>
+          <t>68,47%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>74,07%</t>
+          <t>74,46%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7746,32 +7746,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>677859</t>
+          <t>663028</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>633140</t>
+          <t>633734</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>748755</t>
+          <t>689994</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>62,2%</t>
+          <t>59,48%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>58,09%</t>
+          <t>56,85%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>68,7%</t>
+          <t>61,9%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1332844</t>
+          <t>1369251</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1280548</t>
+          <t>1331499</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1402183</t>
+          <t>1411998</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>66,19%</t>
+          <t>65,15%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>63,59%</t>
+          <t>63,35%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>69,63%</t>
+          <t>67,18%</t>
         </is>
       </c>
     </row>
@@ -7824,17 +7824,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>923840</t>
+          <t>987029</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>923840</t>
+          <t>987029</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>923840</t>
+          <t>987029</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7859,17 +7859,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1089836</t>
+          <t>1114721</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1089836</t>
+          <t>1114721</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1089836</t>
+          <t>1114721</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2013676</t>
+          <t>2101750</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2013676</t>
+          <t>2101750</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2013676</t>
+          <t>2101750</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7941,32 +7941,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>1066102</t>
+          <t>1178305</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>822048</t>
+          <t>1117217</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1173211</t>
+          <t>1240274</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>30,9%</t>
+          <t>33,45%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>23,82%</t>
+          <t>31,71%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>34,0%</t>
+          <t>35,21%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7976,32 +7976,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>1387012</t>
+          <t>1508830</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1124899</t>
+          <t>1458472</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1504516</t>
+          <t>1558289</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>37,97%</t>
+          <t>40,49%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>30,79%</t>
+          <t>39,14%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>41,18%</t>
+          <t>41,82%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>2453114</t>
+          <t>2687135</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2135725</t>
+          <t>2610556</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>2627855</t>
+          <t>2762835</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>34,53%</t>
+          <t>37,07%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>30,06%</t>
+          <t>36,01%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>36,99%</t>
+          <t>38,11%</t>
         </is>
       </c>
     </row>
@@ -8054,32 +8054,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2384444</t>
+          <t>2344489</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2277335</t>
+          <t>2282520</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2628498</t>
+          <t>2405577</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>69,1%</t>
+          <t>66,55%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>66,0%</t>
+          <t>64,79%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>76,18%</t>
+          <t>68,29%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8089,32 +8089,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2266236</t>
+          <t>2217201</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2148732</t>
+          <t>2167742</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2528349</t>
+          <t>2267559</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>62,03%</t>
+          <t>59,51%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>58,82%</t>
+          <t>58,18%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>69,21%</t>
+          <t>60,86%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>4650680</t>
+          <t>4561690</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4475939</t>
+          <t>4485990</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>4968069</t>
+          <t>4638269</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>65,47%</t>
+          <t>62,93%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>63,01%</t>
+          <t>61,89%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>69,94%</t>
+          <t>63,99%</t>
         </is>
       </c>
     </row>
@@ -8167,17 +8167,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3450546</t>
+          <t>3522794</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3450546</t>
+          <t>3522794</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3450546</t>
+          <t>3522794</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8202,17 +8202,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3653248</t>
+          <t>3726031</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3653248</t>
+          <t>3726031</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3653248</t>
+          <t>3726031</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>7103794</t>
+          <t>7248825</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>7103794</t>
+          <t>7248825</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>7103794</t>
+          <t>7248825</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
